--- a/data/trans_orig/IP07C15-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP07C15-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de poder hacer lo que se quiera en el tiempo libre en 2007 (tasa de respuesta: 89,89%)</t>
+          <t>Menores según la frecuencia de poder hacer lo que se quiera en el tiempo libre en 2007 (tasa de respuesta: 89,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10391</t>
+          <t>10827</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21354</t>
+          <t>21496</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>18,83%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>37,14%</t>
+          <t>37,38%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>15174</t>
+          <t>15308</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>27779</t>
+          <t>27217</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>22,52%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>40,87%</t>
+          <t>40,04%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>28906</t>
+          <t>29279</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>45275</t>
+          <t>46476</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>23,34%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>36,08%</t>
+          <t>37,04%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>19518</t>
+          <t>19630</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>31218</t>
+          <t>31470</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>33,94%</t>
+          <t>34,14%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>54,29%</t>
+          <t>54,73%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>22274</t>
+          <t>22651</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>35981</t>
+          <t>35813</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>32,77%</t>
+          <t>33,33%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>52,94%</t>
+          <t>52,69%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>45780</t>
+          <t>45278</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>63574</t>
+          <t>64235</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>36,49%</t>
+          <t>36,09%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>50,67%</t>
+          <t>51,2%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9883</t>
+          <t>9312</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>21149</t>
+          <t>20706</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>16,19%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>36,78%</t>
+          <t>36,01%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>12029</t>
+          <t>11791</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>23015</t>
+          <t>23788</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>33,86%</t>
+          <t>35,0%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>24489</t>
+          <t>24269</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>40704</t>
+          <t>39520</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>19,34%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>32,44%</t>
+          <t>31,5%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>636</t>
+          <t>629</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5582</t>
+          <t>5489</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3736</t>
+          <t>4419</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>732</t>
+          <t>640</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6688</t>
+          <t>6428</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,12%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>29386</t>
+          <t>28388</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>44017</t>
+          <t>43842</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>29,63%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>44,38%</t>
+          <t>44,2%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>24828</t>
+          <t>24602</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>38507</t>
+          <t>38822</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>26,96%</t>
+          <t>26,71%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>41,81%</t>
+          <t>42,15%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>57373</t>
+          <t>58232</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>77926</t>
+          <t>80040</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>29,99%</t>
+          <t>30,44%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>40,74%</t>
+          <t>41,84%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>37578</t>
+          <t>37947</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>52697</t>
+          <t>53665</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>37,89%</t>
+          <t>38,26%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>53,13%</t>
+          <t>54,11%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>33530</t>
+          <t>33932</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>48547</t>
+          <t>48602</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>36,4%</t>
+          <t>36,84%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>52,71%</t>
+          <t>52,77%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>75656</t>
+          <t>75267</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>96638</t>
+          <t>97199</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>39,55%</t>
+          <t>39,35%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>50,52%</t>
+          <t>50,81%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>9810</t>
+          <t>10015</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>21168</t>
+          <t>21260</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>21,44%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>13362</t>
+          <t>12047</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>25322</t>
+          <t>24464</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>27,49%</t>
+          <t>26,56%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>25796</t>
+          <t>25533</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>42635</t>
+          <t>41094</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>22,29%</t>
+          <t>21,48%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>658</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5770</t>
+          <t>6113</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,7 +1774,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>676</t>
+          <t>680</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5495</t>
+          <t>5535</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1982</t>
+          <t>1989</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9229</t>
+          <t>8835</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,7 +1844,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,62%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>21162</t>
+          <t>21132</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>32740</t>
+          <t>32819</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>38,02%</t>
+          <t>37,97%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>58,83%</t>
+          <t>58,97%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>14670</t>
+          <t>14812</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>26258</t>
+          <t>25879</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>23,9%</t>
+          <t>24,13%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>42,78%</t>
+          <t>42,16%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>38631</t>
+          <t>37459</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>54898</t>
+          <t>55258</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>33,01%</t>
+          <t>32,01%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>46,91%</t>
+          <t>47,22%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13794</t>
+          <t>14348</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>24803</t>
+          <t>24567</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>24,79%</t>
+          <t>25,78%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>44,57%</t>
+          <t>44,14%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>24134</t>
+          <t>24399</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>36531</t>
+          <t>36743</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>39,32%</t>
+          <t>39,75%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>59,52%</t>
+          <t>59,86%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>39980</t>
+          <t>41432</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>57330</t>
+          <t>58058</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>34,16%</t>
+          <t>35,4%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>48,99%</t>
+          <t>49,61%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5529</t>
+          <t>5333</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>13698</t>
+          <t>13814</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>24,61%</t>
+          <t>24,82%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>6173</t>
+          <t>6217</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>15714</t>
+          <t>15615</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>25,44%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>13454</t>
+          <t>13734</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>26604</t>
+          <t>26263</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>22,44%</t>
         </is>
       </c>
     </row>
@@ -2476,7 +2476,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3657</t>
+          <t>3725</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2511,7 +2511,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>3624</t>
+          <t>3604</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,08%</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4002</t>
+          <t>4118</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2569,7 +2569,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2624,7 +2624,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>3441</t>
+          <t>4142</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2639,7 +2639,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,54%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>21871</t>
+          <t>22327</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>36426</t>
+          <t>37648</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>27,93%</t>
+          <t>28,51%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>46,52%</t>
+          <t>48,08%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>25122</t>
+          <t>24688</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>39779</t>
+          <t>39853</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>28,51%</t>
+          <t>28,01%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>45,14%</t>
+          <t>45,22%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>51991</t>
+          <t>51836</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>72712</t>
+          <t>71252</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>31,24%</t>
+          <t>31,14%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>43,69%</t>
+          <t>42,81%</t>
         </is>
       </c>
     </row>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>23542</t>
+          <t>22837</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>37262</t>
+          <t>37439</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2907,12 +2907,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>30,06%</t>
+          <t>29,16%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>47,58%</t>
+          <t>47,81%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2927,12 +2927,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>27978</t>
+          <t>27909</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>43902</t>
+          <t>42823</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2942,12 +2942,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>31,75%</t>
+          <t>31,67%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>49,82%</t>
+          <t>48,59%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>55027</t>
+          <t>54958</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>76223</t>
+          <t>75253</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2977,12 +2977,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>33,06%</t>
+          <t>33,02%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>45,8%</t>
+          <t>45,21%</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>10141</t>
+          <t>9899</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>21724</t>
+          <t>23091</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>27,74%</t>
+          <t>29,49%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>12483</t>
+          <t>12645</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>25491</t>
+          <t>24619</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>28,92%</t>
+          <t>27,94%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>25132</t>
+          <t>25051</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>43186</t>
+          <t>42510</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>25,54%</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>719</t>
+          <t>716</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5501</t>
+          <t>6109</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>572</t>
+          <t>569</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>5356</t>
+          <t>5190</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3173,7 +3173,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1792</t>
+          <t>1472</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>8928</t>
+          <t>8772</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,27%</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>4744</t>
+          <t>4983</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3271,7 +3271,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3242</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>646</t>
+          <t>650</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5468</t>
+          <t>5587</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,36%</t>
         </is>
       </c>
     </row>
@@ -3461,12 +3461,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>95466</t>
+          <t>95168</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>121505</t>
+          <t>121168</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3476,12 +3476,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>32,85%</t>
+          <t>32,74%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>41,81%</t>
+          <t>41,69%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>92239</t>
+          <t>90897</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>118130</t>
+          <t>118174</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>29,8%</t>
+          <t>29,36%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>38,16%</t>
+          <t>38,17%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>193121</t>
+          <t>195371</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>230975</t>
+          <t>233352</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>32,17%</t>
+          <t>32,55%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>38,48%</t>
+          <t>38,88%</t>
         </is>
       </c>
     </row>
@@ -3574,12 +3574,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>107433</t>
+          <t>106943</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>133178</t>
+          <t>132901</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3589,12 +3589,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>36,96%</t>
+          <t>36,79%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>45,82%</t>
+          <t>45,73%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3609,12 +3609,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>122217</t>
+          <t>122525</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>148924</t>
+          <t>150091</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>39,48%</t>
+          <t>39,58%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>48,11%</t>
+          <t>48,48%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3644,12 +3644,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>237225</t>
+          <t>235286</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>274964</t>
+          <t>272420</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>39,52%</t>
+          <t>39,2%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>45,81%</t>
+          <t>45,39%</t>
         </is>
       </c>
     </row>
@@ -3687,12 +3687,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>44889</t>
+          <t>43543</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>66232</t>
+          <t>64952</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3702,12 +3702,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>14,98%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3722,12 +3722,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>53193</t>
+          <t>53544</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>75337</t>
+          <t>75168</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3737,12 +3737,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3757,12 +3757,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>102630</t>
+          <t>101741</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>133404</t>
+          <t>133901</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3772,12 +3772,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>22,31%</t>
         </is>
       </c>
     </row>
@@ -3800,12 +3800,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>3227</t>
+          <t>3484</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>12208</t>
+          <t>12362</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3815,12 +3815,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>2620</t>
+          <t>2094</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>10027</t>
+          <t>10058</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3850,12 +3850,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>7437</t>
+          <t>7315</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>18764</t>
+          <t>18224</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3885,12 +3885,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,04%</t>
         </is>
       </c>
     </row>
@@ -3913,62 +3913,62 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
+          <t>668</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>6178</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>0,72%</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>0,23%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>2,13%</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>5589</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>0,72%</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>3553</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>0,21%</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>1,92%</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t>649</t>
-        </is>
-      </c>
-      <c r="L32" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr">
-        <is>
-          <t>3259</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr">
-        <is>
-          <t>0,21%</t>
-        </is>
-      </c>
-      <c r="O32" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3983,12 +3983,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>669</t>
+          <t>685</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>6242</t>
+          <t>6903</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4003,7 +4003,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,15%</t>
         </is>
       </c>
     </row>
@@ -4180,7 +4180,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de poder hacer lo que se quiera en el tiempo libre en 2012 (tasa de respuesta: 95,62%)</t>
+          <t>Menores según la frecuencia de poder hacer lo que se quiera en el tiempo libre en 2012 (tasa de respuesta: 95,62%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4375,12 +4375,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>23546</t>
+          <t>23658</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>37416</t>
+          <t>37159</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4390,12 +4390,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>37,11%</t>
+          <t>37,29%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>58,97%</t>
+          <t>58,57%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>26473</t>
+          <t>26960</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>41015</t>
+          <t>41261</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4425,12 +4425,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>36,78%</t>
+          <t>37,46%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>56,98%</t>
+          <t>57,33%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>54059</t>
+          <t>54431</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>73725</t>
+          <t>74074</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4460,12 +4460,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>39,92%</t>
+          <t>40,19%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>54,44%</t>
+          <t>54,7%</t>
         </is>
       </c>
     </row>
@@ -4488,12 +4488,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14944</t>
+          <t>15239</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>28197</t>
+          <t>27709</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4503,12 +4503,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>23,55%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>44,44%</t>
+          <t>43,67%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4523,12 +4523,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>25169</t>
+          <t>24262</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>38809</t>
+          <t>38093</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4538,12 +4538,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>34,97%</t>
+          <t>33,71%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>53,92%</t>
+          <t>52,92%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4558,12 +4558,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>43127</t>
+          <t>42483</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>62461</t>
+          <t>61224</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4573,12 +4573,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>31,85%</t>
+          <t>31,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>46,12%</t>
+          <t>45,21%</t>
         </is>
       </c>
     </row>
@@ -4601,12 +4601,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8027</t>
+          <t>7405</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>18489</t>
+          <t>17627</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4616,12 +4616,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>29,14%</t>
+          <t>27,78%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4636,12 +4636,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3391</t>
+          <t>3319</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>11548</t>
+          <t>11512</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4671,12 +4671,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>12978</t>
+          <t>13095</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>27801</t>
+          <t>26682</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4686,12 +4686,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>19,7%</t>
         </is>
       </c>
     </row>
@@ -5057,12 +5057,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>39358</t>
+          <t>38872</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>55426</t>
+          <t>54906</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5072,12 +5072,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>40,23%</t>
+          <t>39,73%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>56,65%</t>
+          <t>56,12%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5092,12 +5092,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>27777</t>
+          <t>28886</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>44435</t>
+          <t>43622</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5107,12 +5107,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>29,19%</t>
+          <t>30,35%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>46,69%</t>
+          <t>45,84%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5127,12 +5127,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>71823</t>
+          <t>71874</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>93437</t>
+          <t>93926</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5142,12 +5142,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>37,21%</t>
+          <t>37,24%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>48,41%</t>
+          <t>48,67%</t>
         </is>
       </c>
     </row>
@@ -5170,12 +5170,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>26455</t>
+          <t>26198</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>41065</t>
+          <t>41024</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5185,12 +5185,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>27,04%</t>
+          <t>26,78%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>41,97%</t>
+          <t>41,93%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5205,12 +5205,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>36229</t>
+          <t>36134</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>51992</t>
+          <t>51786</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5220,12 +5220,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>38,07%</t>
+          <t>37,97%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>54,63%</t>
+          <t>54,42%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5240,12 +5240,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>66181</t>
+          <t>66273</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>88258</t>
+          <t>87946</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5255,12 +5255,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>34,29%</t>
+          <t>34,34%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>45,73%</t>
+          <t>45,57%</t>
         </is>
       </c>
     </row>
@@ -5283,12 +5283,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>10877</t>
+          <t>10625</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>22837</t>
+          <t>22574</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5298,12 +5298,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>23,34%</t>
+          <t>23,07%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5318,12 +5318,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>7300</t>
+          <t>7209</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>17610</t>
+          <t>17374</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5353,12 +5353,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>20800</t>
+          <t>21009</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>36355</t>
+          <t>36550</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>18,94%</t>
         </is>
       </c>
     </row>
@@ -5396,12 +5396,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>604</t>
+          <t>602</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5174</t>
+          <t>5042</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5416,7 +5416,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5431,12 +5431,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>663</t>
+          <t>670</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5915</t>
+          <t>6013</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5451,7 +5451,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5466,12 +5466,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1933</t>
+          <t>1923</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9561</t>
+          <t>8460</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5486,7 +5486,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,38%</t>
         </is>
       </c>
     </row>
@@ -5549,7 +5549,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4257</t>
+          <t>4339</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5564,7 +5564,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5584,7 +5584,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3976</t>
+          <t>4645</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5599,7 +5599,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,41%</t>
         </is>
       </c>
     </row>
@@ -5739,12 +5739,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>18696</t>
+          <t>18396</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>31218</t>
+          <t>31542</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5754,12 +5754,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>28,69%</t>
+          <t>28,23%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>47,91%</t>
+          <t>48,4%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5774,12 +5774,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>33456</t>
+          <t>33369</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>45950</t>
+          <t>45861</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5789,12 +5789,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>49,09%</t>
+          <t>48,96%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>67,42%</t>
+          <t>67,29%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5809,12 +5809,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>55366</t>
+          <t>55613</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>73511</t>
+          <t>73378</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>41,53%</t>
+          <t>41,71%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>55,14%</t>
+          <t>55,04%</t>
         </is>
       </c>
     </row>
@@ -5852,12 +5852,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>20057</t>
+          <t>19940</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>32845</t>
+          <t>32581</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5867,12 +5867,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>30,78%</t>
+          <t>30,6%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>50,4%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5887,12 +5887,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>11685</t>
+          <t>11976</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>23033</t>
+          <t>23176</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5902,12 +5902,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>33,79%</t>
+          <t>34,0%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5922,12 +5922,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>34495</t>
+          <t>35027</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>51121</t>
+          <t>51920</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5937,12 +5937,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>25,87%</t>
+          <t>26,27%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>38,34%</t>
+          <t>38,94%</t>
         </is>
       </c>
     </row>
@@ -5965,12 +5965,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>8205</t>
+          <t>8567</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>18676</t>
+          <t>19070</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5980,12 +5980,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>28,66%</t>
+          <t>29,26%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6000,12 +6000,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>6147</t>
+          <t>6316</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>15110</t>
+          <t>15256</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6015,12 +6015,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>22,38%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6035,12 +6035,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>17096</t>
+          <t>17052</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>30503</t>
+          <t>30309</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>22,73%</t>
         </is>
       </c>
     </row>
@@ -6083,7 +6083,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4274</t>
+          <t>3940</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6098,7 +6098,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6118,7 +6118,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3969</t>
+          <t>3916</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6133,7 +6133,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>611</t>
+          <t>604</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>6181</t>
+          <t>5601</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,2%</t>
         </is>
       </c>
     </row>
@@ -6196,7 +6196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3335</t>
+          <t>3459</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6211,7 +6211,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6266,7 +6266,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>3409</t>
+          <t>3408</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6421,12 +6421,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>22975</t>
+          <t>23109</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>37712</t>
+          <t>37829</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6436,12 +6436,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>26,8%</t>
+          <t>26,96%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>43,99%</t>
+          <t>44,13%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>23000</t>
+          <t>22754</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>38308</t>
+          <t>37896</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>25,32%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>42,63%</t>
+          <t>42,17%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>49687</t>
+          <t>50282</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>71326</t>
+          <t>72381</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6506,12 +6506,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>28,3%</t>
+          <t>28,64%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>40,62%</t>
+          <t>41,22%</t>
         </is>
       </c>
     </row>
@@ -6534,12 +6534,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>29433</t>
+          <t>29346</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>45263</t>
+          <t>44645</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6549,12 +6549,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>34,33%</t>
+          <t>34,23%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>52,8%</t>
+          <t>52,08%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6569,12 +6569,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>28408</t>
+          <t>28330</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>43051</t>
+          <t>44137</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6584,12 +6584,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>31,62%</t>
+          <t>31,53%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>47,91%</t>
+          <t>49,12%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>62514</t>
+          <t>61749</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>85053</t>
+          <t>84437</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6619,12 +6619,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>35,6%</t>
+          <t>35,17%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>48,44%</t>
+          <t>48,09%</t>
         </is>
       </c>
     </row>
@@ -6647,12 +6647,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>11299</t>
+          <t>11785</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>25879</t>
+          <t>24968</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6662,12 +6662,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>30,19%</t>
+          <t>29,13%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6682,12 +6682,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>15099</t>
+          <t>15092</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>28836</t>
+          <t>28919</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6702,7 +6702,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>32,09%</t>
+          <t>32,18%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6717,12 +6717,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>29861</t>
+          <t>29996</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>48639</t>
+          <t>48726</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6732,12 +6732,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>17,08%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>27,7%</t>
+          <t>27,75%</t>
         </is>
       </c>
     </row>
@@ -6765,7 +6765,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5616</t>
+          <t>6754</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6780,7 +6780,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6795,12 +6795,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>671</t>
+          <t>664</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>6571</t>
+          <t>5850</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6810,12 +6810,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6830,12 +6830,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>782</t>
+          <t>1054</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>8621</t>
+          <t>7864</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6845,12 +6845,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,48%</t>
         </is>
       </c>
     </row>
@@ -7103,12 +7103,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>118201</t>
+          <t>117926</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>145946</t>
+          <t>146257</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7118,12 +7118,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>37,86%</t>
+          <t>37,78%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>46,75%</t>
+          <t>46,85%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>126032</t>
+          <t>126017</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>154576</t>
+          <t>155017</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7158,7 +7158,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>47,54%</t>
+          <t>47,67%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>250190</t>
+          <t>251055</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>291622</t>
+          <t>290972</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7188,12 +7188,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>39,26%</t>
+          <t>39,39%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>45,76%</t>
+          <t>45,65%</t>
         </is>
       </c>
     </row>
@@ -7216,12 +7216,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>103897</t>
+          <t>103404</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>131432</t>
+          <t>131845</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7231,12 +7231,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>33,28%</t>
+          <t>33,12%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>42,1%</t>
+          <t>42,23%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7251,12 +7251,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>113221</t>
+          <t>112581</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>143189</t>
+          <t>142107</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7266,12 +7266,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>34,82%</t>
+          <t>34,62%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>44,04%</t>
+          <t>43,7%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>224819</t>
+          <t>224334</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>266603</t>
+          <t>263905</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7301,12 +7301,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>35,28%</t>
+          <t>35,2%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>41,83%</t>
+          <t>41,41%</t>
         </is>
       </c>
     </row>
@@ -7329,12 +7329,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>47479</t>
+          <t>47712</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>70896</t>
+          <t>70141</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7344,12 +7344,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>22,47%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7364,12 +7364,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>40009</t>
+          <t>40027</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>61385</t>
+          <t>60723</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7379,12 +7379,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>18,68%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7399,12 +7399,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>93029</t>
+          <t>92629</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>124151</t>
+          <t>124462</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>19,53%</t>
         </is>
       </c>
     </row>
@@ -7442,12 +7442,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1340</t>
+          <t>1799</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>8601</t>
+          <t>8622</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7457,7 +7457,7 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
@@ -7477,12 +7477,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>2740</t>
+          <t>2719</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>10974</t>
+          <t>10381</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7497,7 +7497,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>5757</t>
+          <t>6182</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>16058</t>
+          <t>16056</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7527,7 +7527,7 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -7560,7 +7560,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>4108</t>
+          <t>3815</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7575,7 +7575,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7595,7 +7595,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>4597</t>
+          <t>5279</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7610,7 +7610,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7630,7 +7630,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>6057</t>
+          <t>5382</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7645,7 +7645,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,84%</t>
         </is>
       </c>
     </row>
@@ -7822,7 +7822,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de poder hacer lo que se quiera en el tiempo libre en 2016 (tasa de respuesta: 95,47%)</t>
+          <t>Menores según la frecuencia de poder hacer lo que se quiera en el tiempo libre en 2016 (tasa de respuesta: 95,47%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8017,12 +8017,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15866</t>
+          <t>15643</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>28794</t>
+          <t>28424</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8032,12 +8032,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>22,99%</t>
+          <t>22,67%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>41,73%</t>
+          <t>41,19%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>20314</t>
+          <t>19829</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>34958</t>
+          <t>33423</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8067,12 +8067,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>28,59%</t>
+          <t>27,91%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>49,21%</t>
+          <t>47,05%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8087,12 +8087,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>39497</t>
+          <t>39262</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>58357</t>
+          <t>58289</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8102,12 +8102,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>28,2%</t>
+          <t>28,03%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>41,67%</t>
+          <t>41,62%</t>
         </is>
       </c>
     </row>
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>26862</t>
+          <t>26568</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>40572</t>
+          <t>40275</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8145,12 +8145,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>38,93%</t>
+          <t>38,5%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>58,8%</t>
+          <t>58,37%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8165,12 +8165,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>23222</t>
+          <t>24171</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>38563</t>
+          <t>38038</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8180,12 +8180,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>32,69%</t>
+          <t>34,02%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>54,28%</t>
+          <t>53,54%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8200,12 +8200,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>54007</t>
+          <t>54020</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>74002</t>
+          <t>73853</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8215,12 +8215,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>38,56%</t>
+          <t>38,57%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>52,84%</t>
+          <t>52,73%</t>
         </is>
       </c>
     </row>
@@ -8243,12 +8243,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8402</t>
+          <t>8308</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>19589</t>
+          <t>20242</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8258,12 +8258,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>28,39%</t>
+          <t>29,33%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8278,12 +8278,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5364</t>
+          <t>5442</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>15314</t>
+          <t>16041</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8293,12 +8293,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>22,58%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8313,12 +8313,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>16209</t>
+          <t>16206</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>31309</t>
+          <t>32065</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8333,7 +8333,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>22,9%</t>
         </is>
       </c>
     </row>
@@ -8391,12 +8391,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1512</t>
+          <t>1509</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8737</t>
+          <t>9532</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8406,12 +8406,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8426,12 +8426,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1487</t>
+          <t>1498</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8608</t>
+          <t>8694</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,21%</t>
         </is>
       </c>
     </row>
@@ -8699,12 +8699,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>26177</t>
+          <t>26547</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>41891</t>
+          <t>41582</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8714,12 +8714,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>25,8%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>40,71%</t>
+          <t>40,41%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8734,12 +8734,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>25995</t>
+          <t>25081</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>41437</t>
+          <t>41008</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8749,12 +8749,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>25,31%</t>
+          <t>24,42%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>40,34%</t>
+          <t>39,92%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8769,12 +8769,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>55465</t>
+          <t>56035</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>77960</t>
+          <t>78494</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>27,25%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>37,91%</t>
+          <t>38,17%</t>
         </is>
       </c>
     </row>
@@ -8812,12 +8812,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>41755</t>
+          <t>41555</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>58119</t>
+          <t>57793</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8827,12 +8827,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>40,58%</t>
+          <t>40,39%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>56,48%</t>
+          <t>56,17%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8847,12 +8847,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>46733</t>
+          <t>46762</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>62452</t>
+          <t>63354</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8862,12 +8862,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>45,49%</t>
+          <t>45,52%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>60,8%</t>
+          <t>61,67%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8882,12 +8882,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>91690</t>
+          <t>93036</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>115630</t>
+          <t>116185</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>44,59%</t>
+          <t>45,25%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>56,23%</t>
+          <t>56,5%</t>
         </is>
       </c>
     </row>
@@ -8925,12 +8925,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>10740</t>
+          <t>11145</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>22474</t>
+          <t>22994</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8940,12 +8940,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8960,12 +8960,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>8364</t>
+          <t>7843</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>19073</t>
+          <t>18796</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8975,12 +8975,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>21583</t>
+          <t>21194</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>37868</t>
+          <t>37417</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9010,12 +9010,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>18,2%</t>
         </is>
       </c>
     </row>
@@ -9043,7 +9043,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>4890</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9058,7 +9058,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9073,12 +9073,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>708</t>
+          <t>715</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6185</t>
+          <t>6248</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9088,12 +9088,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9108,12 +9108,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1413</t>
+          <t>1499</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8592</t>
+          <t>8396</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9123,12 +9123,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,08%</t>
         </is>
       </c>
     </row>
@@ -9156,7 +9156,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3782</t>
+          <t>4340</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9171,7 +9171,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9226,7 +9226,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4310</t>
+          <t>3769</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9241,7 +9241,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>1,83%</t>
         </is>
       </c>
     </row>
@@ -9381,12 +9381,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>25770</t>
+          <t>26188</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>39118</t>
+          <t>39645</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9396,12 +9396,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>36,86%</t>
+          <t>37,46%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>55,96%</t>
+          <t>56,71%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9416,12 +9416,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>26543</t>
+          <t>25753</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>40385</t>
+          <t>40286</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>35,88%</t>
+          <t>34,82%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>54,6%</t>
+          <t>54,46%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9451,12 +9451,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>56039</t>
+          <t>56886</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>75992</t>
+          <t>75233</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9466,12 +9466,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>38,95%</t>
+          <t>39,54%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>52,82%</t>
+          <t>52,29%</t>
         </is>
       </c>
     </row>
@@ -9494,12 +9494,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>21309</t>
+          <t>21122</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>34730</t>
+          <t>34453</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9509,12 +9509,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>30,48%</t>
+          <t>30,21%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>49,68%</t>
+          <t>49,28%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9529,12 +9529,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>25723</t>
+          <t>26451</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>39731</t>
+          <t>40637</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>34,78%</t>
+          <t>35,76%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>53,71%</t>
+          <t>54,94%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9564,12 +9564,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>51563</t>
+          <t>50909</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>70471</t>
+          <t>70051</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9579,12 +9579,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>35,84%</t>
+          <t>35,38%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>48,98%</t>
+          <t>48,69%</t>
         </is>
       </c>
     </row>
@@ -9607,12 +9607,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5668</t>
+          <t>5516</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>15521</t>
+          <t>15650</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9622,12 +9622,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>22,39%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9642,12 +9642,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3459</t>
+          <t>3500</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>12047</t>
+          <t>12050</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9657,7 +9657,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>10891</t>
+          <t>11156</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>23009</t>
+          <t>23551</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9692,12 +9692,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>16,37%</t>
         </is>
       </c>
     </row>
@@ -9760,7 +9760,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5379</t>
+          <t>5250</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9775,7 +9775,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9795,7 +9795,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>6400</t>
+          <t>6363</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9810,7 +9810,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,42%</t>
         </is>
       </c>
     </row>
@@ -10063,12 +10063,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>22537</t>
+          <t>22304</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>38715</t>
+          <t>38067</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10078,12 +10078,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>21,69%</t>
+          <t>21,47%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>37,27%</t>
+          <t>36,64%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>24415</t>
+          <t>25239</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>39711</t>
+          <t>40934</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10113,12 +10113,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>25,36%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>39,9%</t>
+          <t>41,13%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10133,12 +10133,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>51862</t>
+          <t>50923</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>74904</t>
+          <t>73550</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10148,12 +10148,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>25,5%</t>
+          <t>25,03%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>36,82%</t>
+          <t>36,16%</t>
         </is>
       </c>
     </row>
@@ -10176,12 +10176,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>40367</t>
+          <t>40436</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>57923</t>
+          <t>58537</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10191,12 +10191,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>38,86%</t>
+          <t>38,92%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>55,76%</t>
+          <t>56,35%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>38731</t>
+          <t>38449</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>55525</t>
+          <t>55535</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10226,12 +10226,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>38,91%</t>
+          <t>38,63%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>55,79%</t>
+          <t>55,8%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10246,12 +10246,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>84922</t>
+          <t>85646</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>108508</t>
+          <t>109926</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10261,12 +10261,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>41,75%</t>
+          <t>42,11%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>53,34%</t>
+          <t>54,04%</t>
         </is>
       </c>
     </row>
@@ -10289,12 +10289,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>15100</t>
+          <t>14945</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>28950</t>
+          <t>28664</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10304,12 +10304,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>27,87%</t>
+          <t>27,59%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10324,12 +10324,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>12997</t>
+          <t>12891</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>26015</t>
+          <t>25700</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10339,12 +10339,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>26,14%</t>
+          <t>25,82%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10359,12 +10359,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>31062</t>
+          <t>30892</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>50262</t>
+          <t>50629</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10374,12 +10374,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>24,71%</t>
+          <t>24,89%</t>
         </is>
       </c>
     </row>
@@ -10402,12 +10402,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>635</t>
+          <t>625</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5636</t>
+          <t>5595</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10417,12 +10417,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10442,7 +10442,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>5877</t>
+          <t>5189</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10457,7 +10457,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10472,12 +10472,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1357</t>
+          <t>1354</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>8219</t>
+          <t>7339</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10492,7 +10492,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,61%</t>
         </is>
       </c>
     </row>
@@ -10520,7 +10520,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>4727</t>
+          <t>3344</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10535,7 +10535,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10590,7 +10590,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4811</t>
+          <t>4146</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10605,7 +10605,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,04%</t>
         </is>
       </c>
     </row>
@@ -10745,12 +10745,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>103515</t>
+          <t>103850</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>133354</t>
+          <t>132908</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10760,12 +10760,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>29,94%</t>
+          <t>30,04%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>38,58%</t>
+          <t>38,45%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10780,12 +10780,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>108236</t>
+          <t>111280</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>139929</t>
+          <t>140384</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10795,12 +10795,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>31,17%</t>
+          <t>32,04%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>40,29%</t>
+          <t>40,43%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10815,12 +10815,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>223257</t>
+          <t>223750</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>265214</t>
+          <t>263444</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>32,22%</t>
+          <t>32,29%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>38,27%</t>
+          <t>38,02%</t>
         </is>
       </c>
     </row>
@@ -10858,12 +10858,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>145558</t>
+          <t>143869</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>175350</t>
+          <t>174849</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10873,12 +10873,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>42,11%</t>
+          <t>41,62%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>50,72%</t>
+          <t>50,58%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10893,12 +10893,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>150357</t>
+          <t>148698</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>182542</t>
+          <t>179339</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10908,12 +10908,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>43,3%</t>
+          <t>42,82%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>52,57%</t>
+          <t>51,64%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10928,12 +10928,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>305288</t>
+          <t>302145</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>346157</t>
+          <t>346191</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10943,12 +10943,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>44,06%</t>
+          <t>43,6%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>49,95%</t>
+          <t>49,96%</t>
         </is>
       </c>
     </row>
@@ -10971,12 +10971,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>48887</t>
+          <t>49761</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>73757</t>
+          <t>74435</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>21,53%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11006,12 +11006,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>37799</t>
+          <t>38312</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>59081</t>
+          <t>59031</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11021,12 +11021,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11041,12 +11041,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>93726</t>
+          <t>93865</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>123467</t>
+          <t>126684</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11056,12 +11056,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>18,28%</t>
         </is>
       </c>
     </row>
@@ -11084,12 +11084,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>1387</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>8311</t>
+          <t>8678</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11099,12 +11099,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11119,12 +11119,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>4666</t>
+          <t>4572</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>14860</t>
+          <t>14799</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11134,12 +11134,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11154,12 +11154,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>7599</t>
+          <t>7379</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>20240</t>
+          <t>20683</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11169,12 +11169,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,98%</t>
         </is>
       </c>
     </row>
@@ -11197,82 +11197,82 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
+          <t>613</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>5823</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>0,6%</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>0,18%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>1,68%</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr">
+        <is>
+          <t>2067</t>
+        </is>
+      </c>
+      <c r="S32" s="2" t="inlineStr">
+        <is>
           <t>615</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>5858</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>0,6%</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>0,18%</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>1,69%</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L32" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O32" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P32" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q32" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R32" s="2" t="inlineStr">
-        <is>
-          <t>2067</t>
-        </is>
-      </c>
-      <c r="S32" s="2" t="inlineStr">
-        <is>
-          <t>617</t>
-        </is>
-      </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>5775</t>
+          <t>5894</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11287,7 +11287,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,85%</t>
         </is>
       </c>
     </row>
@@ -11464,7 +11464,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de poder hacer lo que se quiera en el tiempo libre en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Menores según la frecuencia de poder hacer lo que se quiera en el tiempo libre en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -11659,7 +11659,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7367</t>
+          <t>7526</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -11674,7 +11674,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>24,14%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -11694,12 +11694,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16586</t>
+          <t>16365</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>36539</t>
+          <t>37048</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -11709,12 +11709,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>34,54%</t>
+          <t>34,08%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>76,09%</t>
+          <t>77,15%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -11729,12 +11729,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>26800</t>
+          <t>26255</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>54153</t>
+          <t>52646</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -11744,12 +11744,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>33,84%</t>
+          <t>33,15%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>68,38%</t>
+          <t>66,48%</t>
         </is>
       </c>
     </row>
@@ -11772,12 +11772,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12446</t>
+          <t>12903</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>21663</t>
+          <t>21752</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -11787,12 +11787,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>39,93%</t>
+          <t>41,39%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>69,49%</t>
+          <t>69,78%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11807,12 +11807,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8196</t>
+          <t>8179</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>24390</t>
+          <t>24750</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -11822,12 +11822,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>50,79%</t>
+          <t>51,54%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11842,12 +11842,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>20078</t>
+          <t>21901</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>43569</t>
+          <t>43733</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -11857,12 +11857,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>27,66%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>55,02%</t>
+          <t>55,22%</t>
         </is>
       </c>
     </row>
@@ -11890,7 +11890,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7882</t>
+          <t>7263</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -11905,7 +11905,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>23,3%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11920,12 +11920,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1962</t>
+          <t>2207</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10834</t>
+          <t>11288</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11935,12 +11935,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>23,51%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11955,12 +11955,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>3811</t>
+          <t>3893</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>14946</t>
+          <t>14143</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11970,12 +11970,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>17,86%</t>
         </is>
       </c>
     </row>
@@ -12341,12 +12341,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13320</t>
+          <t>13137</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24469</t>
+          <t>24800</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -12356,12 +12356,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>24,84%</t>
+          <t>24,49%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>45,62%</t>
+          <t>46,24%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -12376,12 +12376,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>31973</t>
+          <t>32062</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>52160</t>
+          <t>51989</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -12391,12 +12391,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>31,11%</t>
+          <t>31,2%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>50,75%</t>
+          <t>50,58%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -12411,12 +12411,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>49016</t>
+          <t>49981</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>72678</t>
+          <t>73095</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -12426,12 +12426,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>31,34%</t>
+          <t>31,96%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>46,47%</t>
+          <t>46,73%</t>
         </is>
       </c>
     </row>
@@ -12454,12 +12454,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>19952</t>
+          <t>19819</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>32094</t>
+          <t>32498</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -12469,12 +12469,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>37,2%</t>
+          <t>36,95%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>59,84%</t>
+          <t>60,59%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -12489,12 +12489,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>31854</t>
+          <t>32474</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>51429</t>
+          <t>52968</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -12504,12 +12504,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>30,99%</t>
+          <t>31,6%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>50,04%</t>
+          <t>51,54%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -12524,12 +12524,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>56445</t>
+          <t>55787</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>79358</t>
+          <t>79537</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -12539,12 +12539,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>36,09%</t>
+          <t>35,67%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>50,74%</t>
+          <t>50,85%</t>
         </is>
       </c>
     </row>
@@ -12567,12 +12567,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4346</t>
+          <t>3845</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>12792</t>
+          <t>13339</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -12582,12 +12582,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>24,87%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -12602,12 +12602,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>8731</t>
+          <t>9021</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>30754</t>
+          <t>32498</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -12617,12 +12617,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>29,92%</t>
+          <t>31,62%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -12637,12 +12637,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>15681</t>
+          <t>15768</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>39207</t>
+          <t>40065</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>25,62%</t>
         </is>
       </c>
     </row>
@@ -12680,12 +12680,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>529</t>
+          <t>524</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4694</t>
+          <t>4615</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -12695,12 +12695,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -12750,12 +12750,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>521</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4505</t>
+          <t>4674</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -12765,12 +12765,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,99%</t>
         </is>
       </c>
     </row>
@@ -12833,7 +12833,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>7453</t>
+          <t>7411</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -12848,7 +12848,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12868,7 +12868,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>8359</t>
+          <t>8166</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -12883,7 +12883,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,22%</t>
         </is>
       </c>
     </row>
@@ -13023,12 +13023,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5942</t>
+          <t>7549</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>37198</t>
+          <t>38101</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -13038,12 +13038,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>51,53%</t>
+          <t>52,78%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -13058,12 +13058,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>30744</t>
+          <t>29713</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>47651</t>
+          <t>46956</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -13073,12 +13073,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>47,31%</t>
+          <t>45,73%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>73,33%</t>
+          <t>72,26%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -13093,12 +13093,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>33641</t>
+          <t>32397</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>80851</t>
+          <t>79342</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -13108,12 +13108,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>58,95%</t>
+          <t>57,85%</t>
         </is>
       </c>
     </row>
@@ -13136,12 +13136,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>24441</t>
+          <t>23662</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>64068</t>
+          <t>60925</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -13151,12 +13151,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>33,86%</t>
+          <t>32,78%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>88,76%</t>
+          <t>84,4%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -13171,12 +13171,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>12624</t>
+          <t>13151</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>29421</t>
+          <t>28444</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -13186,12 +13186,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>20,24%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>45,28%</t>
+          <t>43,77%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -13206,12 +13206,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>41470</t>
+          <t>42150</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>98781</t>
+          <t>96387</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -13221,12 +13221,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>30,23%</t>
+          <t>30,73%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>72,02%</t>
+          <t>70,27%</t>
         </is>
       </c>
     </row>
@@ -13249,12 +13249,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1592</t>
+          <t>1750</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>12597</t>
+          <t>13840</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -13264,12 +13264,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>19,17%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -13284,12 +13284,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1941</t>
+          <t>1939</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>10526</t>
+          <t>10230</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -13299,12 +13299,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -13319,12 +13319,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>4991</t>
+          <t>5367</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>18485</t>
+          <t>19058</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -13334,12 +13334,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>13,89%</t>
         </is>
       </c>
     </row>
@@ -13402,7 +13402,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4444</t>
+          <t>4394</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -13417,7 +13417,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -13437,7 +13437,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4819</t>
+          <t>4281</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -13452,7 +13452,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,12%</t>
         </is>
       </c>
     </row>
@@ -13705,12 +13705,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>16112</t>
+          <t>16022</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>28675</t>
+          <t>27843</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -13720,12 +13720,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>30,13%</t>
+          <t>29,96%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>53,62%</t>
+          <t>52,06%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13740,12 +13740,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>17383</t>
+          <t>17359</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>30298</t>
+          <t>30506</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -13755,12 +13755,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>30,84%</t>
+          <t>30,79%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>53,75%</t>
+          <t>54,12%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13775,12 +13775,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>36942</t>
+          <t>37146</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>54943</t>
+          <t>54665</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -13790,12 +13790,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>33,63%</t>
+          <t>33,81%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>50,01%</t>
+          <t>49,76%</t>
         </is>
       </c>
     </row>
@@ -13818,12 +13818,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>18659</t>
+          <t>19439</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>31708</t>
+          <t>31613</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -13833,12 +13833,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>34,89%</t>
+          <t>36,35%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>59,29%</t>
+          <t>59,11%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -13853,12 +13853,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>17025</t>
+          <t>17244</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>30533</t>
+          <t>30310</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -13868,12 +13868,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>30,2%</t>
+          <t>30,59%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>54,16%</t>
+          <t>53,77%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -13888,12 +13888,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>40815</t>
+          <t>40756</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>59040</t>
+          <t>58193</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -13903,12 +13903,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>37,15%</t>
+          <t>37,1%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>53,74%</t>
+          <t>52,97%</t>
         </is>
       </c>
     </row>
@@ -13931,12 +13931,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2500</t>
+          <t>2498</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>10786</t>
+          <t>10335</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13951,7 +13951,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13966,12 +13966,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3175</t>
+          <t>3265</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>12045</t>
+          <t>11994</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13981,12 +13981,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>21,37%</t>
+          <t>21,28%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -14001,12 +14001,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>7270</t>
+          <t>7284</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>20041</t>
+          <t>18739</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -14016,12 +14016,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>17,06%</t>
         </is>
       </c>
     </row>
@@ -14049,7 +14049,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4661</t>
+          <t>3897</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -14064,7 +14064,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -14084,7 +14084,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>6106</t>
+          <t>6505</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -14099,7 +14099,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -14114,12 +14114,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>839</t>
+          <t>861</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>7809</t>
+          <t>7515</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -14129,12 +14129,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>6,84%</t>
         </is>
       </c>
     </row>
@@ -14387,12 +14387,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>46697</t>
+          <t>47231</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>89588</t>
+          <t>90425</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -14402,12 +14402,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>22,44%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>42,57%</t>
+          <t>42,96%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -14422,12 +14422,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>114784</t>
+          <t>113396</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>153356</t>
+          <t>153859</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>42,18%</t>
+          <t>41,67%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>56,35%</t>
+          <t>56,54%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -14457,12 +14457,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>167640</t>
+          <t>167157</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>232476</t>
+          <t>229081</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -14472,12 +14472,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>34,74%</t>
+          <t>34,64%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>48,17%</t>
+          <t>47,47%</t>
         </is>
       </c>
     </row>
@@ -14500,12 +14500,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>93164</t>
+          <t>92540</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>152018</t>
+          <t>148821</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -14515,12 +14515,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>44,26%</t>
+          <t>43,97%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>72,23%</t>
+          <t>70,71%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -14535,12 +14535,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>83358</t>
+          <t>84163</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>117789</t>
+          <t>118129</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -14550,12 +14550,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>30,63%</t>
+          <t>30,93%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>43,28%</t>
+          <t>43,41%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -14570,12 +14570,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>186849</t>
+          <t>187706</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>267336</t>
+          <t>260105</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -14585,12 +14585,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>38,72%</t>
+          <t>38,89%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>55,39%</t>
+          <t>53,89%</t>
         </is>
       </c>
     </row>
@@ -14613,12 +14613,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>13111</t>
+          <t>13519</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>31684</t>
+          <t>32573</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -14628,12 +14628,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14648,12 +14648,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>24150</t>
+          <t>23627</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>51082</t>
+          <t>51531</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -14663,12 +14663,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14683,12 +14683,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>41285</t>
+          <t>40544</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>75240</t>
+          <t>74204</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -14698,12 +14698,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>15,38%</t>
         </is>
       </c>
     </row>
@@ -14726,12 +14726,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>613</t>
+          <t>620</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>6544</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -14746,7 +14746,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -14761,12 +14761,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>880</t>
+          <t>893</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>7948</t>
+          <t>8594</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -14776,12 +14776,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -14796,12 +14796,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>2594</t>
+          <t>2530</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>11543</t>
+          <t>10885</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -14811,12 +14811,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,26%</t>
         </is>
       </c>
     </row>
@@ -14879,7 +14879,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>7371</t>
+          <t>8175</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -14894,7 +14894,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -14914,7 +14914,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>7994</t>
+          <t>8309</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -14929,7 +14929,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,72%</t>
         </is>
       </c>
     </row>
